--- a/dataset/construct/dataset_splits/tum/fold5.xlsx
+++ b/dataset/construct/dataset_splits/tum/fold5.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN53"/>
+  <dimension ref="A1:AK51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,185 +446,170 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>AFPRE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CABGPRE</t>
+          <t>LVEFPRE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>AFPRE</t>
+          <t>PREDILATION</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LVEFPRE</t>
+          <t>CT_ValScNCC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>NTPROBNPPRE</t>
+          <t>CT_ValScRCC</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PREDILATION</t>
+          <t>CT_ValScLCC</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScNCC</t>
+          <t>CT_ValvScTot</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScRCC</t>
+          <t>CT_AnnScNCC</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScLCC</t>
+          <t>CT_AnnScRCC</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValvScTot</t>
+          <t>CT_AnnScLCC</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScNCC</t>
+          <t>CT_AnnScTot</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScRCC</t>
+          <t>CT_LVOTScNCC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScLCC</t>
+          <t>CT_LVOTScRCC</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScTot</t>
+          <t>CT_LVOTScLCC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScNCC</t>
+          <t>CT_LVOTScTot</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScRCC</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScLCC</t>
+          <t>CT_AnnMean</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScTot</t>
+          <t>ECC_INDEX</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>CT_Peri_Deri</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnMean</t>
+          <t>CT_Area_Deri</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>ECC_INDEX</t>
+          <t>nyha2</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>CT_Peri_Deri</t>
+          <t>nyha3</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>CT_Area_Deri</t>
+          <t>nyha4</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>nyha2</t>
+          <t>model1</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>nyha3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>nyha4</t>
+          <t>model3</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>model1</t>
+          <t>model4</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>model7</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>model8</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>model4</t>
+          <t>brand2</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>model7</t>
+          <t>brand8</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>model8</t>
+          <t>QRSADM</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>brand2</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>brand8</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>QRSADM</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PQADM</t>
         </is>
@@ -632,7 +617,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2031</v>
+        <v>556</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -640,88 +625,88 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>85.6764691865034</v>
+        <v>78.32835766978479</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>25.8264462809917</v>
       </c>
       <c r="E2" t="n">
-        <v>27.7777777777777</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>60</v>
+        <v>855</v>
       </c>
       <c r="I2" t="n">
-        <v>882</v>
+        <v>523</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>457</v>
       </c>
       <c r="K2" t="n">
-        <v>423.4</v>
+        <v>1835</v>
       </c>
       <c r="L2" t="n">
-        <v>142.6</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>389.7</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>955.7</v>
+        <v>77</v>
       </c>
       <c r="O2" t="n">
-        <v>114.3</v>
+        <v>77</v>
       </c>
       <c r="P2" t="n">
-        <v>55.1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>29.1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>198.5</v>
+        <v>15</v>
       </c>
       <c r="S2" t="n">
-        <v>65.40000000000001</v>
+        <v>15</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>27.2</v>
+        <v>24.95</v>
       </c>
       <c r="V2" t="n">
-        <v>92.59999999999999</v>
+        <v>0.31</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>26.1013496307614</v>
       </c>
       <c r="X2" t="n">
-        <v>28.85</v>
+        <v>24.9992044677091</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.235474006116208</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
-        <v>29.4435956200662</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>28.5191036537487</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2" t="n">
         <v>0</v>
@@ -739,22 +724,15 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="AK2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>208</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
+        <v>184</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>704</v>
+        <v>1147</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -762,83 +740,85 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>85.76208647045399</v>
+        <v>77.6437583656552</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>35.7559561895442</v>
       </c>
       <c r="E3" t="n">
-        <v>24.609375</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>60</v>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>80</v>
+      </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="K3" t="n">
-        <v>514.4</v>
+        <v>208</v>
       </c>
       <c r="L3" t="n">
-        <v>174.8</v>
+        <v>10</v>
       </c>
       <c r="M3" t="n">
-        <v>420.7</v>
+        <v>14</v>
       </c>
       <c r="N3" t="n">
-        <v>1109.9</v>
+        <v>30</v>
       </c>
       <c r="O3" t="n">
-        <v>5.4</v>
+        <v>54</v>
       </c>
       <c r="P3" t="n">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>68.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>87.3</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>5.7</v>
+        <v>21.35</v>
       </c>
       <c r="V3" t="n">
-        <v>5.7</v>
+        <v>0.16</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>21.3267125031831</v>
       </c>
       <c r="X3" t="n">
-        <v>22.85</v>
+        <v>21.1969216859002</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.319852941176471</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.7140310669722</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.9332496617824</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
@@ -853,28 +833,21 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>146</v>
-      </c>
-      <c r="AN3" t="inlineStr"/>
+        <v>90</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>471</v>
+        <v>1705</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -882,79 +855,79 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>75.0402101553984</v>
+        <v>85.11794274596291</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>23.0400201994697</v>
       </c>
       <c r="E4" t="n">
-        <v>24.2105958514995</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>55</v>
+        <v>1413.6</v>
       </c>
       <c r="I4" t="n">
-        <v>200</v>
+        <v>1288</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>1236</v>
       </c>
       <c r="K4" t="n">
-        <v>464</v>
+        <v>3937.6</v>
       </c>
       <c r="L4" t="n">
-        <v>640</v>
+        <v>379</v>
       </c>
       <c r="M4" t="n">
-        <v>720</v>
+        <v>126</v>
       </c>
       <c r="N4" t="n">
-        <v>1824</v>
+        <v>492</v>
       </c>
       <c r="O4" t="n">
-        <v>6</v>
+        <v>997</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="Q4" t="n">
-        <v>99</v>
+        <v>5.5</v>
       </c>
       <c r="R4" t="n">
-        <v>105</v>
+        <v>650</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>851.5</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>30.15</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>29.8892284186402</v>
       </c>
       <c r="X4" t="n">
-        <v>25.8</v>
+        <v>29.6417868004739</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>25.6557168321874</v>
+        <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>24.7175864208069</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -966,39 +939,30 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="AK4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>190</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>643</v>
+        <v>2598</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1006,79 +970,79 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>77.2277739752072</v>
+        <v>86.49229824194489</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>23.3843537414965</v>
       </c>
       <c r="E5" t="n">
-        <v>33.802055164954</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>45</v>
+        <v>262</v>
       </c>
       <c r="I5" t="n">
-        <v>14500</v>
+        <v>392</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>248</v>
       </c>
       <c r="K5" t="n">
-        <v>289</v>
+        <v>902</v>
       </c>
       <c r="L5" t="n">
-        <v>594</v>
+        <v>19</v>
       </c>
       <c r="M5" t="n">
-        <v>377</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1260</v>
+        <v>50</v>
       </c>
       <c r="O5" t="n">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="P5" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>89</v>
+        <v>40</v>
       </c>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>24.55</v>
       </c>
       <c r="V5" t="n">
-        <v>13</v>
+        <v>0.17</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>25.1464222052457</v>
       </c>
       <c r="X5" t="n">
-        <v>27.95</v>
+        <v>24.7484641173191</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.253125</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>27.6928953399542</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>26.8169675507093</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1099,30 +1063,21 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="AK5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>124</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>198</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1997</v>
+        <v>493</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1130,41 +1085,43 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>80.8359181940325</v>
+        <v>86.04058293406339</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>24.765625</v>
       </c>
       <c r="E6" t="n">
-        <v>23.309053069719</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>60</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>978</v>
+      </c>
+      <c r="I6" t="n">
+        <v>246</v>
+      </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>288</v>
       </c>
       <c r="K6" t="n">
-        <v>91.8</v>
+        <v>1512</v>
       </c>
       <c r="L6" t="n">
-        <v>81.7</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>52.5</v>
+        <v>12</v>
       </c>
       <c r="N6" t="n">
-        <v>226</v>
+        <v>139</v>
       </c>
       <c r="O6" t="n">
-        <v>18.2</v>
+        <v>151</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -1173,34 +1130,34 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>18.2</v>
+        <v>37</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>22.8</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>23.2683982683983</v>
       </c>
       <c r="X6" t="n">
-        <v>21.4</v>
+        <v>23.1211849536588</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.216666666666667</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>22.0588235294118</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.710123730909</v>
+        <v>1</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1215,7 +1172,7 @@
         <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1227,24 +1184,13 @@
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>84</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>154</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="AK6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>473</v>
+        <v>2192</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1252,40 +1198,40 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>88.3022824612772</v>
+        <v>83.62327093948841</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>26.9896193771626</v>
       </c>
       <c r="E7" t="n">
-        <v>26.218820861678</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>60</v>
+        <v>80.7</v>
       </c>
       <c r="I7" t="n">
-        <v>4730</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>32.9</v>
       </c>
       <c r="K7" t="n">
-        <v>218</v>
+        <v>113.6</v>
       </c>
       <c r="L7" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>512</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1303,28 +1249,28 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>21.6</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.36</v>
       </c>
       <c r="W7" t="n">
-        <v>2</v>
+        <v>21.6768525592055</v>
       </c>
       <c r="X7" t="n">
-        <v>20.75</v>
+        <v>20.6555825335006</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.270833333333333</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>21.3267125031831</v>
+        <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>20.8945249963572</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -1339,7 +1285,7 @@
         <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1351,113 +1297,102 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>94</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>188</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="AK7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>515</v>
+        <v>570</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>pacer</t>
+          <t>no event</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>78.3007491063959</v>
+        <v>80.10493763784319</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>31.2213039485766</v>
       </c>
       <c r="E8" t="n">
-        <v>23.2356317012401</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>60</v>
       </c>
       <c r="I8" t="n">
-        <v>3550</v>
+        <v>137</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>96</v>
       </c>
       <c r="K8" t="n">
-        <v>629</v>
+        <v>293</v>
       </c>
       <c r="L8" t="n">
-        <v>562</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>620</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1811</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>27.2</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>27.6928953399542</v>
       </c>
       <c r="X8" t="n">
-        <v>27.75</v>
+        <v>26.5066584133226</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.292307692307692</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>27.947542653425</v>
+        <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>26.973142863685</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1475,24 +1410,13 @@
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>242</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="AK8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1736</v>
+        <v>2169</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1500,91 +1424,91 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>86.46788494689081</v>
+        <v>79.1083821646767</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>23.1836734693877</v>
       </c>
       <c r="E9" t="n">
-        <v>24.8579545454545</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>60</v>
+        <v>696.4</v>
       </c>
       <c r="I9" t="n">
-        <v>4130</v>
+        <v>556.8</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>561.3</v>
       </c>
       <c r="K9" t="n">
-        <v>187.8</v>
+        <v>1814.5</v>
       </c>
       <c r="L9" t="n">
-        <v>186.2</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>239</v>
+        <v>44.3</v>
       </c>
       <c r="N9" t="n">
-        <v>613</v>
+        <v>52.8</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>25.25</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>25.6557168321874</v>
       </c>
       <c r="X9" t="n">
-        <v>27.2</v>
+        <v>24.2129335077053</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.192691029900332</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>27.3745861981156</v>
+        <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>26.9117274486368</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -1599,22 +1523,13 @@
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN9" t="inlineStr"/>
+        <v>96</v>
+      </c>
+      <c r="AK9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>361</v>
+        <v>604</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1622,44 +1537,46 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>78.027219623799</v>
+        <v>89.1044661190965</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>23.046875</v>
       </c>
       <c r="E10" t="n">
-        <v>26.6097125450789</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>60</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
+        <v>1163</v>
+      </c>
+      <c r="I10" t="n">
+        <v>612</v>
+      </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>798</v>
       </c>
       <c r="K10" t="n">
-        <v>276</v>
+        <v>2573</v>
       </c>
       <c r="L10" t="n">
-        <v>295</v>
+        <v>86</v>
       </c>
       <c r="M10" t="n">
-        <v>161</v>
+        <v>24</v>
       </c>
       <c r="N10" t="n">
-        <v>732</v>
+        <v>30</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1668,40 +1585,40 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>25.75</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>25.8785332314744</v>
       </c>
       <c r="X10" t="n">
-        <v>24.05</v>
+        <v>25.4533139190353</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.282142857142857</v>
+        <v>1</v>
       </c>
       <c r="Z10" t="n">
-        <v>24.5098039215686</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>23.7993692983298</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1710,119 +1627,110 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AK10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>84</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>156</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>656</v>
+        <v>941</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no event</t>
+          <t>pacer</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>86.7305080868</v>
+        <v>72.25305355920599</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>20.8325296091971</v>
       </c>
       <c r="E11" t="n">
-        <v>21.3406795224977</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>21</v>
+        <v>877</v>
       </c>
       <c r="I11" t="n">
-        <v>15200</v>
+        <v>110</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="K11" t="n">
-        <v>286.8</v>
+        <v>1071</v>
       </c>
       <c r="L11" t="n">
-        <v>357.2</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>166.4</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>810.4</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>12.2</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>28.3</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>46.2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>5</v>
+        <v>23.9</v>
       </c>
       <c r="V11" t="n">
-        <v>5</v>
+        <v>0.25</v>
       </c>
       <c r="W11" t="n">
-        <v>2</v>
+        <v>24.1914947797301</v>
       </c>
       <c r="X11" t="n">
-        <v>23.65</v>
+        <v>23.5574721962474</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.15234375</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>23.7458619811561</v>
+        <v>1</v>
       </c>
       <c r="AA11" t="n">
-        <v>23.5115010765807</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1831,7 +1739,7 @@
         <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -1840,25 +1748,18 @@
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>148</v>
-      </c>
-      <c r="AN11" t="inlineStr"/>
+        <v>188</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2121</v>
+        <v>496</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1866,121 +1767,112 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>82.77180653788631</v>
+        <v>74.640161672624</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>29.7265160523186</v>
       </c>
       <c r="E12" t="n">
-        <v>23.0300453514739</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
+        <v>696</v>
+      </c>
+      <c r="I12" t="n">
+        <v>233</v>
+      </c>
+      <c r="J12" t="n">
+        <v>339</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1268</v>
+      </c>
+      <c r="L12" t="n">
+        <v>131</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" t="n">
+        <v>133</v>
+      </c>
+      <c r="P12" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
         <v>45</v>
       </c>
-      <c r="I12" t="n">
-        <v>5520</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>56.6</v>
-      </c>
-      <c r="M12" t="n">
-        <v>67.3</v>
-      </c>
-      <c r="N12" t="n">
-        <v>123.9</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>27.2</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="n">
-        <v>2</v>
+        <v>26.7379679144385</v>
       </c>
       <c r="X12" t="n">
-        <v>22.8</v>
+        <v>26.4345313179585</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.197628458498024</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.5681181563535</v>
+        <v>1</v>
       </c>
       <c r="AA12" t="n">
-        <v>22.1942730679895</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>166</v>
-      </c>
-      <c r="AN12" t="inlineStr"/>
+        <v>112</v>
+      </c>
+      <c r="AK12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2598</v>
+        <v>2302</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1988,77 +1880,79 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>86.49229824194489</v>
+        <v>91.7489835728953</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>21.2244897959183</v>
       </c>
       <c r="E13" t="n">
-        <v>23.3843537414965</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>60</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
+        <v>216.5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>32.1</v>
+      </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>262</v>
+        <v>340</v>
       </c>
       <c r="L13" t="n">
-        <v>392</v>
+        <v>22.2</v>
       </c>
       <c r="M13" t="n">
-        <v>248</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>902</v>
+        <v>6.1</v>
       </c>
       <c r="O13" t="n">
-        <v>19</v>
+        <v>28.3</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>40</v>
+        <v>21.5</v>
       </c>
       <c r="V13" t="n">
-        <v>40</v>
+        <v>0.19</v>
       </c>
       <c r="W13" t="n">
-        <v>1</v>
+        <v>21.8678380443086</v>
       </c>
       <c r="X13" t="n">
-        <v>24.55</v>
+        <v>21.3763064498772</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.167910447761194</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>25.1464222052457</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>24.7484641173191</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -2076,7 +1970,7 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
         <v>0</v>
@@ -2085,24 +1979,15 @@
         <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>102</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>134</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2419</v>
+        <v>515</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2110,82 +1995,82 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>83.00703576951349</v>
+        <v>78.3007491063959</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>23.2356317012401</v>
       </c>
       <c r="E14" t="n">
-        <v>24.1588179685585</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>40</v>
+        <v>629</v>
       </c>
       <c r="I14" t="n">
-        <v>1960</v>
+        <v>562</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>620</v>
       </c>
       <c r="K14" t="n">
-        <v>441.3</v>
+        <v>1811</v>
       </c>
       <c r="L14" t="n">
-        <v>341.5</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>36.7</v>
+        <v>27</v>
       </c>
       <c r="N14" t="n">
-        <v>819.5</v>
+        <v>12</v>
       </c>
       <c r="O14" t="n">
-        <v>36.3</v>
+        <v>39</v>
       </c>
       <c r="P14" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>63.8</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>27.75</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="W14" t="n">
-        <v>1</v>
+        <v>27.947542653425</v>
       </c>
       <c r="X14" t="n">
-        <v>22.95</v>
+        <v>26.973142863685</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.171314741035857</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>23.4275528393175</v>
+        <v>1</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.0743446333452</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2194,39 +2079,30 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>98</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>234</v>
+        <v>242</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>922</v>
+        <v>1356</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2234,91 +2110,91 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>75.0324815258448</v>
+        <v>78.99659071032021</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>23.9868703446534</v>
       </c>
       <c r="E15" t="n">
-        <v>26.4721074380165</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>60</v>
+        <v>404.3</v>
       </c>
       <c r="I15" t="n">
-        <v>1120</v>
+        <v>263.5</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>383.3</v>
       </c>
       <c r="K15" t="n">
-        <v>280</v>
+        <v>1051.1</v>
       </c>
       <c r="L15" t="n">
-        <v>391</v>
+        <v>36.6</v>
       </c>
       <c r="M15" t="n">
-        <v>306</v>
+        <v>6.3</v>
       </c>
       <c r="N15" t="n">
-        <v>977</v>
+        <v>13.7</v>
       </c>
       <c r="O15" t="n">
-        <v>16</v>
+        <v>56.59999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>27.95</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="W15" t="n">
-        <v>1</v>
+        <v>27.7565571683219</v>
       </c>
       <c r="X15" t="n">
-        <v>26.5</v>
+        <v>27.2874765576698</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.22742474916388</v>
+        <v>1</v>
       </c>
       <c r="Z15" t="n">
-        <v>27.3745861981156</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>26.7218716216114</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -2333,22 +2209,13 @@
         <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>86</v>
-      </c>
-      <c r="AN15" t="inlineStr"/>
+        <v>94</v>
+      </c>
+      <c r="AK15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>348</v>
+        <v>2123</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2356,163 +2223,158 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>88.94842941161561</v>
+        <v>77.31505558090601</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>22.8930740819877</v>
       </c>
       <c r="E16" t="n">
-        <v>22.5878330942278</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>42</v>
-      </c>
-      <c r="I16" t="inlineStr"/>
+        <v>590.9</v>
+      </c>
+      <c r="I16" t="n">
+        <v>480</v>
+      </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>205.4</v>
       </c>
       <c r="K16" t="n">
-        <v>114</v>
+        <v>1276.3</v>
       </c>
       <c r="L16" t="n">
-        <v>107</v>
+        <v>13.8</v>
       </c>
       <c r="M16" t="n">
-        <v>336</v>
+        <v>75</v>
       </c>
       <c r="N16" t="n">
-        <v>557</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>26</v>
+        <v>88.8</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>260</v>
+        <v>10.3</v>
       </c>
       <c r="R16" t="n">
-        <v>286</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>10.3</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>174</v>
+        <v>29.3</v>
       </c>
       <c r="V16" t="n">
-        <v>180</v>
+        <v>0.25</v>
       </c>
       <c r="W16" t="n">
-        <v>1</v>
+        <v>30.143875732111</v>
       </c>
       <c r="X16" t="n">
-        <v>23.65</v>
+        <v>28.9751548801889</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.286231884057971</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>23.554876496053</v>
+        <v>1</v>
       </c>
       <c r="AA16" t="n">
-        <v>23.0660688205498</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="AK16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>98</v>
-      </c>
-      <c r="AN16" t="inlineStr"/>
+        <v>176</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1331</v>
+        <v>1672</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no event</t>
+          <t>pacer</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>77.67647340101909</v>
+        <v>85.7315332281289</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>26.0789715335169</v>
       </c>
       <c r="E17" t="n">
-        <v>20.7612456747404</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>122</v>
       </c>
       <c r="I17" t="n">
-        <v>1030</v>
+        <v>52</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="K17" t="n">
-        <v>296</v>
+        <v>238</v>
       </c>
       <c r="L17" t="n">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>555</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -2521,40 +2383,40 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>24.2</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="W17" t="n">
-        <v>2</v>
+        <v>23.8731856378915</v>
       </c>
       <c r="X17" t="n">
-        <v>21.85</v>
+        <v>23.3675988578761</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.244979919678715</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>21.9633307868602</v>
+        <v>1</v>
       </c>
       <c r="AA17" t="n">
-        <v>21.4654366757236</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2566,33 +2428,24 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH17" t="n">
         <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>92</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>180</v>
+        <v>272</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>562</v>
+        <v>2359</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2600,94 +2453,94 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>85.7368640200776</v>
+        <v>84.26097786270191</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>24.2214532871972</v>
       </c>
       <c r="E18" t="n">
-        <v>20.8979591836734</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>60</v>
+        <v>376.3</v>
       </c>
       <c r="I18" t="n">
-        <v>3410</v>
+        <v>779</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>320.1</v>
       </c>
       <c r="K18" t="n">
-        <v>77</v>
+        <v>1475.4</v>
       </c>
       <c r="L18" t="n">
-        <v>62</v>
+        <v>140.7</v>
       </c>
       <c r="M18" t="n">
-        <v>33</v>
+        <v>42.8</v>
       </c>
       <c r="N18" t="n">
-        <v>172</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>9</v>
+        <v>272.6</v>
       </c>
       <c r="P18" t="n">
-        <v>20</v>
+        <v>34.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>39</v>
+        <v>3.1</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>24.35</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="W18" t="n">
-        <v>2</v>
+        <v>24.5734657499363</v>
       </c>
       <c r="X18" t="n">
-        <v>22.25</v>
+        <v>23.6975361509812</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.145833333333333</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>22.2816399286988</v>
+        <v>1</v>
       </c>
       <c r="AA18" t="n">
-        <v>22.1655797488585</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -2699,104 +2552,95 @@
         <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="AK18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>270</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>598</v>
+        <v>579</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>pacer</t>
+          <t>no event</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>80.29658529165719</v>
+        <v>79.1056030876873</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>25.390625</v>
       </c>
       <c r="E19" t="n">
-        <v>17.0068027210884</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>60</v>
+        <v>282</v>
       </c>
       <c r="I19" t="n">
-        <v>1630</v>
+        <v>283</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>266</v>
       </c>
       <c r="K19" t="n">
-        <v>32</v>
+        <v>831</v>
       </c>
       <c r="L19" t="n">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="M19" t="n">
+        <v>41</v>
+      </c>
+      <c r="N19" t="n">
         <v>77</v>
       </c>
-      <c r="N19" t="n">
-        <v>238</v>
-      </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="P19" t="n">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="Q19" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="T19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>69</v>
+        <v>24.4</v>
       </c>
       <c r="V19" t="n">
-        <v>74</v>
+        <v>0.28</v>
       </c>
       <c r="W19" t="n">
-        <v>2</v>
+        <v>24.5098039215686</v>
       </c>
       <c r="X19" t="n">
-        <v>19.8</v>
+        <v>23.8260951566085</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.285714285714286</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>19.7351667939903</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>19.1461601132455</v>
+        <v>1</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -2811,36 +2655,27 @@
         <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>98</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>180</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>636</v>
+        <v>326</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2848,79 +2683,79 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>81.9098752756864</v>
+        <v>83.6231034362562</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>24.0238086700849</v>
       </c>
       <c r="E20" t="n">
-        <v>31.25</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>50</v>
+        <v>196.4</v>
       </c>
       <c r="I20" t="n">
-        <v>2600</v>
+        <v>35.3</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>124.8</v>
       </c>
       <c r="K20" t="n">
-        <v>607.7</v>
+        <v>356.5</v>
       </c>
       <c r="L20" t="n">
-        <v>229.5</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>268.5</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1105.7</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>26.8</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>20.3</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>47.1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>22.9</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W20" t="n">
-        <v>2</v>
+        <v>23.2365673542144</v>
       </c>
       <c r="X20" t="n">
-        <v>24.45</v>
+        <v>22.6484228950307</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.08984375</v>
+        <v>1</v>
       </c>
       <c r="Z20" t="n">
-        <v>24.3824802648332</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>24.1734751727661</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -2944,27 +2779,16 @@
         <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>94</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>146</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="AK20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>983</v>
+        <v>1019</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2972,79 +2796,79 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>74.1668630694349</v>
+        <v>84.97033370725281</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>30.1109905115367</v>
       </c>
       <c r="E21" t="n">
-        <v>25.4580659041199</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>60</v>
+        <v>156</v>
       </c>
       <c r="I21" t="n">
-        <v>1060</v>
+        <v>152</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>253</v>
       </c>
       <c r="K21" t="n">
-        <v>993</v>
+        <v>561</v>
       </c>
       <c r="L21" t="n">
-        <v>491</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>960</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2444</v>
+        <v>98</v>
       </c>
       <c r="O21" t="n">
-        <v>227</v>
+        <v>98</v>
       </c>
       <c r="P21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>370</v>
+        <v>96</v>
       </c>
       <c r="S21" t="n">
-        <v>151</v>
+        <v>96</v>
       </c>
       <c r="T21" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>17</v>
+        <v>24.3</v>
       </c>
       <c r="V21" t="n">
-        <v>206</v>
+        <v>0.23</v>
       </c>
       <c r="W21" t="n">
-        <v>1</v>
+        <v>24.1914947797301</v>
       </c>
       <c r="X21" t="n">
-        <v>24.35</v>
+        <v>23.6114412754479</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.169172932330827</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>23.8731856378915</v>
+        <v>1</v>
       </c>
       <c r="AA21" t="n">
-        <v>23.6921643870788</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3062,116 +2886,107 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH21" t="n">
         <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>136</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>118</v>
+        <v>180</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>528</v>
+        <v>704</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>no event</t>
+          <t>pacer</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>84.2009601490608</v>
+        <v>85.76208647045399</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>24.609375</v>
       </c>
       <c r="E22" t="n">
-        <v>20.5498866213151</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>60</v>
+        <v>514.4</v>
       </c>
       <c r="I22" t="n">
-        <v>786</v>
+        <v>174.8</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>420.7</v>
       </c>
       <c r="K22" t="n">
-        <v>118.2</v>
+        <v>1109.9</v>
       </c>
       <c r="L22" t="n">
-        <v>74.2</v>
+        <v>5.4</v>
       </c>
       <c r="M22" t="n">
-        <v>82.59999999999999</v>
+        <v>13.8</v>
       </c>
       <c r="N22" t="n">
-        <v>275</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>35.2</v>
+        <v>87.3</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>41.7</v>
+        <v>5.7</v>
       </c>
       <c r="S22" t="n">
-        <v>14.2</v>
+        <v>5.7</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
-        <v>13.8</v>
+        <v>22.85</v>
       </c>
       <c r="V22" t="n">
-        <v>28</v>
+        <v>0.32</v>
       </c>
       <c r="W22" t="n">
-        <v>2</v>
+        <v>23.7140310669722</v>
       </c>
       <c r="X22" t="n">
-        <v>22.9</v>
+        <v>22.9332496617824</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.297397769516729</v>
+        <v>1</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.8545963840081</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>22.0850401322991</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3195,104 +3010,93 @@
         <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>74</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>156</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="AK22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1025</v>
+        <v>512</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>pacer</t>
+          <t>no event</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>85.2467825500038</v>
+        <v>85.7615408015819</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>25.9106843468983</v>
       </c>
       <c r="E23" t="n">
-        <v>30.3460743801652</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>42</v>
+        <v>248</v>
       </c>
       <c r="I23" t="n">
-        <v>3370</v>
+        <v>269</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="K23" t="n">
-        <v>242.8</v>
+        <v>615</v>
       </c>
       <c r="L23" t="n">
-        <v>371.3</v>
+        <v>31</v>
       </c>
       <c r="M23" t="n">
-        <v>285.3</v>
+        <v>55</v>
       </c>
       <c r="N23" t="n">
-        <v>899.4</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>72.3</v>
+        <v>86</v>
       </c>
       <c r="P23" t="n">
-        <v>106.7</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>85.3</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>264.3</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>22.6</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>53.2</v>
+        <v>22.8</v>
       </c>
       <c r="V23" t="n">
-        <v>75.8</v>
+        <v>0.32</v>
       </c>
       <c r="W23" t="n">
-        <v>1</v>
+        <v>23.554876496053</v>
       </c>
       <c r="X23" t="n">
-        <v>26.9</v>
+        <v>22.7045529015462</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.16382252559727</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>27.1836007130125</v>
+        <v>1</v>
       </c>
       <c r="AA23" t="n">
-        <v>26.8217134966894</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3319,22 +3123,13 @@
         <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>86</v>
-      </c>
-      <c r="AN23" t="inlineStr"/>
+        <v>78</v>
+      </c>
+      <c r="AK23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2636</v>
+        <v>1312</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3342,77 +3137,79 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>85.0193633229396</v>
+        <v>77.89833593175651</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>20.6575400021007</v>
       </c>
       <c r="E24" t="n">
-        <v>27.1314117909923</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>51</v>
-      </c>
-      <c r="I24" t="inlineStr"/>
+        <v>253.9</v>
+      </c>
+      <c r="I24" t="n">
+        <v>78.8</v>
+      </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>126.2</v>
       </c>
       <c r="K24" t="n">
-        <v>560</v>
+        <v>458.9</v>
       </c>
       <c r="L24" t="n">
-        <v>472</v>
+        <v>26.8</v>
       </c>
       <c r="M24" t="n">
-        <v>603</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1635</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>15</v>
+        <v>102.9</v>
       </c>
       <c r="P24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>69</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>22.3</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W24" t="n">
-        <v>1</v>
+        <v>22.886427298192</v>
       </c>
       <c r="X24" t="n">
-        <v>28.4</v>
+        <v>22.5272697980512</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.230529595015576</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>27.8838808250573</v>
+        <v>1</v>
       </c>
       <c r="AA24" t="n">
-        <v>27.2524701589629</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3439,24 +3236,15 @@
         <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>124</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>557</v>
+        <v>520</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -3464,79 +3252,79 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>91.0891873906761</v>
+        <v>91.96256179177119</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>24.4646016033723</v>
       </c>
       <c r="E25" t="n">
-        <v>29.3575219240468</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>55</v>
+        <v>503</v>
       </c>
       <c r="I25" t="n">
-        <v>2840</v>
+        <v>648</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>259</v>
       </c>
       <c r="K25" t="n">
-        <v>11.9</v>
+        <v>1410</v>
       </c>
       <c r="L25" t="n">
-        <v>30.6</v>
+        <v>20</v>
       </c>
       <c r="M25" t="n">
-        <v>170.9</v>
+        <v>7</v>
       </c>
       <c r="N25" t="n">
-        <v>213.4</v>
+        <v>163</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>84.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>84.90000000000001</v>
+        <v>152</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>62.7</v>
+        <v>23.95</v>
       </c>
       <c r="V25" t="n">
-        <v>62.7</v>
+        <v>0.27</v>
       </c>
       <c r="W25" t="n">
-        <v>2</v>
+        <v>23.8731856378915</v>
       </c>
       <c r="X25" t="n">
-        <v>22.1</v>
+        <v>22.9831467948561</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.217741935483871</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>22.1224853577795</v>
+        <v>1</v>
       </c>
       <c r="AA25" t="n">
-        <v>21.8532914302955</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -3551,34 +3339,25 @@
         <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>82</v>
-      </c>
-      <c r="AN25" t="inlineStr"/>
+        <v>105</v>
+      </c>
+      <c r="AK25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>485</v>
+        <v>2482</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3586,94 +3365,94 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>89.0005646817248</v>
+        <v>78.8975567850534</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>27.7176852352623</v>
       </c>
       <c r="E26" t="n">
-        <v>22.0385674931129</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>60</v>
+        <v>314.2</v>
       </c>
       <c r="I26" t="n">
-        <v>4370</v>
+        <v>160.8</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>322.6</v>
       </c>
       <c r="K26" t="n">
-        <v>510</v>
+        <v>797.6</v>
       </c>
       <c r="L26" t="n">
-        <v>296</v>
+        <v>11</v>
       </c>
       <c r="M26" t="n">
-        <v>359</v>
+        <v>13.9</v>
       </c>
       <c r="N26" t="n">
-        <v>1165</v>
+        <v>25.9</v>
       </c>
       <c r="O26" t="n">
-        <v>35</v>
+        <v>50.8</v>
       </c>
       <c r="P26" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>205</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>232</v>
+        <v>23.25</v>
       </c>
       <c r="V26" t="n">
-        <v>246</v>
+        <v>0.25</v>
       </c>
       <c r="W26" t="n">
-        <v>2</v>
+        <v>23.3638910109498</v>
       </c>
       <c r="X26" t="n">
-        <v>22.05</v>
+        <v>22.8665507818143</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.221774193548387</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>22.5999490705373</v>
+        <v>1</v>
       </c>
       <c r="AA26" t="n">
-        <v>22.1655797488585</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -3685,67 +3464,60 @@
         <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>138</v>
-      </c>
-      <c r="AN26" t="inlineStr"/>
+        <v>98</v>
+      </c>
+      <c r="AK26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2192</v>
+        <v>519</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>pacer</t>
+          <t>no event</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>83.62327093948841</v>
+        <v>77.5943455776105</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>34.2058298631766</v>
       </c>
       <c r="E27" t="n">
-        <v>26.9896193771626</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>30</v>
-      </c>
-      <c r="I27" t="inlineStr"/>
+        <v>376.3</v>
+      </c>
+      <c r="I27" t="n">
+        <v>275.7</v>
+      </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>276.5</v>
       </c>
       <c r="K27" t="n">
-        <v>80.7</v>
+        <v>928.5</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>25.6</v>
       </c>
       <c r="M27" t="n">
-        <v>32.9</v>
+        <v>33.7</v>
       </c>
       <c r="N27" t="n">
-        <v>113.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>123.9</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>22.9</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -3754,37 +3526,37 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>22.9</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>24.55</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="W27" t="n">
-        <v>2</v>
+        <v>24.859943977591</v>
       </c>
       <c r="X27" t="n">
-        <v>21.6</v>
+        <v>24.5496573149696</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.357414448669202</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>21.6768525592055</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>20.6555825335006</v>
+        <v>1</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -3805,22 +3577,13 @@
         <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>122</v>
-      </c>
-      <c r="AN27" t="inlineStr"/>
+        <v>160</v>
+      </c>
+      <c r="AK27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>320</v>
+        <v>611</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -3828,83 +3591,85 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>80.3924023373134</v>
+        <v>86.12057761046469</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>25.390625</v>
       </c>
       <c r="E28" t="n">
-        <v>22.189349112426</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
+        <v>431</v>
+      </c>
+      <c r="I28" t="n">
+        <v>64</v>
+      </c>
+      <c r="J28" t="n">
+        <v>153</v>
+      </c>
+      <c r="K28" t="n">
+        <v>648</v>
+      </c>
+      <c r="L28" t="n">
         <v>50</v>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="n">
-        <v>1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>160</v>
-      </c>
-      <c r="L28" t="n">
-        <v>145</v>
-      </c>
       <c r="M28" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="N28" t="n">
-        <v>322</v>
+        <v>64</v>
       </c>
       <c r="O28" t="n">
-        <v>15</v>
+        <v>147</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>22.9</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="W28" t="n">
-        <v>2</v>
+        <v>23.6822001527884</v>
       </c>
       <c r="X28" t="n">
-        <v>20.75</v>
+        <v>22.5639660829322</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.248945147679325</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>21.3267125031831</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>20.6802165106906</v>
+        <v>1</v>
       </c>
       <c r="AB28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
@@ -3913,36 +3678,25 @@
         <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>96</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>156</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="AK28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1492</v>
+        <v>2308</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3950,85 +3704,85 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>80.88521056734351</v>
+        <v>76.85541314928891</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>28.2828282828282</v>
       </c>
       <c r="E29" t="n">
-        <v>27.6816608996539</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>60</v>
+        <v>387.4</v>
       </c>
       <c r="I29" t="n">
-        <v>900</v>
+        <v>356.4</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>395.4</v>
       </c>
       <c r="K29" t="n">
-        <v>804.3</v>
+        <v>1139.2</v>
       </c>
       <c r="L29" t="n">
-        <v>478.3</v>
+        <v>119.7</v>
       </c>
       <c r="M29" t="n">
-        <v>399.3</v>
+        <v>53.2</v>
       </c>
       <c r="N29" t="n">
-        <v>1681.9</v>
+        <v>175.5</v>
       </c>
       <c r="O29" t="n">
-        <v>34.8</v>
+        <v>348.4</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>14.9</v>
       </c>
       <c r="Q29" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>42.4</v>
+        <v>127.4</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>142.3</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>23.05</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W29" t="n">
-        <v>1</v>
+        <v>22.8545963840081</v>
       </c>
       <c r="X29" t="n">
-        <v>25.45</v>
+        <v>22.1741916431478</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.188612099644128</v>
+        <v>1</v>
       </c>
       <c r="Z29" t="n">
-        <v>25.6238859180036</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>25.3430608104398</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -4040,7 +3794,7 @@
         <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
         <v>0</v>
@@ -4049,102 +3803,95 @@
         <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AK29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>86</v>
-      </c>
-      <c r="AN29" t="inlineStr"/>
+        <v>256</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>579</v>
+        <v>506</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>no event</t>
+          <t>pacer</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>79.1056030876873</v>
+        <v>83.28082363677851</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>24.6913580246913</v>
       </c>
       <c r="E30" t="n">
-        <v>25.390625</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>50</v>
+        <v>349.5</v>
       </c>
       <c r="I30" t="n">
-        <v>5640</v>
+        <v>410.7</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>277.3</v>
       </c>
       <c r="K30" t="n">
-        <v>282</v>
+        <v>1037.5</v>
       </c>
       <c r="L30" t="n">
-        <v>283</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>266</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>831</v>
+        <v>14.5</v>
       </c>
       <c r="O30" t="n">
-        <v>158</v>
+        <v>14.5</v>
       </c>
       <c r="P30" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>24.9</v>
       </c>
       <c r="V30" t="n">
-        <v>17</v>
+        <v>0.25</v>
       </c>
       <c r="W30" t="n">
-        <v>2</v>
+        <v>24.9554367201426</v>
       </c>
       <c r="X30" t="n">
-        <v>24.4</v>
+        <v>24.4118755484088</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.281690140845071</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>24.5098039215686</v>
+        <v>1</v>
       </c>
       <c r="AA30" t="n">
-        <v>23.8260951566085</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
@@ -4153,7 +3900,7 @@
         <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4171,113 +3918,104 @@
         <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="AK30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM30" t="n">
         <v>100</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>146</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2642</v>
+        <v>2178</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>no event</t>
+          <t>pacer</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>78.0542406266636</v>
+        <v>79.7736672624027</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>30.0432622977087</v>
       </c>
       <c r="E31" t="n">
-        <v>26.5021162137573</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>59</v>
+        <v>545.4</v>
       </c>
       <c r="I31" t="n">
-        <v>1460</v>
+        <v>113.2</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>43.6</v>
       </c>
       <c r="K31" t="n">
-        <v>323</v>
+        <v>702.2</v>
       </c>
       <c r="L31" t="n">
-        <v>476</v>
+        <v>62.3</v>
       </c>
       <c r="M31" t="n">
-        <v>477</v>
+        <v>7.3</v>
       </c>
       <c r="N31" t="n">
-        <v>1276</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="P31" t="n">
-        <v>8</v>
+        <v>16.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>16.8</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>25.1</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="W31" t="n">
-        <v>2</v>
+        <v>25.3374076903489</v>
       </c>
       <c r="X31" t="n">
-        <v>24.15</v>
+        <v>24.9966585942398</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.256317689530686</v>
+        <v>1</v>
       </c>
       <c r="Z31" t="n">
-        <v>24.3188184364655</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>23.866127828619</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
         <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4286,7 +4024,7 @@
         <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
         <v>0</v>
@@ -4295,113 +4033,102 @@
         <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>128</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>191</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="AK31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>672</v>
+        <v>516</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>no event</t>
+          <t>pacer</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>84.077751159784</v>
+        <v>82.09534185109131</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>29.0256076388888</v>
       </c>
       <c r="E32" t="n">
-        <v>23.3234180638182</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>60</v>
+        <v>797</v>
       </c>
       <c r="I32" t="n">
-        <v>5030</v>
+        <v>410</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>424</v>
       </c>
       <c r="K32" t="n">
-        <v>701.4</v>
+        <v>1631</v>
       </c>
       <c r="L32" t="n">
-        <v>213.8</v>
+        <v>133</v>
       </c>
       <c r="M32" t="n">
-        <v>169.8</v>
+        <v>44</v>
       </c>
       <c r="N32" t="n">
-        <v>1085</v>
+        <v>70</v>
       </c>
       <c r="O32" t="n">
-        <v>35.9</v>
+        <v>247</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>33.3</v>
+        <v>9</v>
       </c>
       <c r="R32" t="n">
-        <v>69.2</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>6.9</v>
+        <v>25</v>
       </c>
       <c r="V32" t="n">
-        <v>6.9</v>
+        <v>0.26</v>
       </c>
       <c r="W32" t="n">
-        <v>1</v>
+        <v>25.1464222052457</v>
       </c>
       <c r="X32" t="n">
-        <v>23.75</v>
+        <v>24.6143810163112</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.220973782771536</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>24.3188184364655</v>
+        <v>1</v>
       </c>
       <c r="AA32" t="n">
-        <v>23.7002215763568</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4413,110 +4140,99 @@
         <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>82</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>170</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="AK32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2302</v>
+        <v>588</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>pacer</t>
+          <t>no event</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>91.7489835728953</v>
+        <v>86.977426040003</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>30.7173999207292</v>
       </c>
       <c r="E33" t="n">
-        <v>21.2244897959183</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G33" t="n">
         <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>60</v>
+        <v>556</v>
       </c>
       <c r="I33" t="n">
-        <v>270</v>
+        <v>582</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>318</v>
       </c>
       <c r="K33" t="n">
-        <v>216.5</v>
+        <v>1456</v>
       </c>
       <c r="L33" t="n">
-        <v>32.1</v>
+        <v>91</v>
       </c>
       <c r="M33" t="n">
-        <v>91.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>340</v>
+        <v>45</v>
       </c>
       <c r="O33" t="n">
-        <v>22.2</v>
+        <v>136</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q33" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>28.3</v>
+        <v>20</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>26.65</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="W33" t="n">
-        <v>1</v>
+        <v>27.2472625413802</v>
       </c>
       <c r="X33" t="n">
-        <v>21.5</v>
+        <v>26.8406888888731</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.185654008438819</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>21.8678380443086</v>
+        <v>1</v>
       </c>
       <c r="AA33" t="n">
-        <v>21.3763064498772</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
@@ -4528,119 +4244,110 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>86</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>176</v>
+        <v>122</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>466</v>
+        <v>563</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>pacer</t>
+          <t>no event</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>71.8237397964357</v>
+        <v>78.34722792607801</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>28.6726260752234</v>
       </c>
       <c r="E34" t="n">
-        <v>43.3862813295564</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>60</v>
+        <v>264</v>
       </c>
       <c r="I34" t="n">
-        <v>920</v>
+        <v>278</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>531</v>
       </c>
       <c r="K34" t="n">
-        <v>432</v>
+        <v>1073</v>
       </c>
       <c r="L34" t="n">
-        <v>414</v>
+        <v>10</v>
       </c>
       <c r="M34" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>948</v>
+        <v>12</v>
       </c>
       <c r="O34" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="P34" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>23.35</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="W34" t="n">
-        <v>2</v>
+        <v>23.8731856378915</v>
       </c>
       <c r="X34" t="n">
-        <v>21.45</v>
+        <v>23.4111342451446</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.32421875</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>21.3267125031831</v>
+        <v>1</v>
       </c>
       <c r="AA34" t="n">
-        <v>20.6494194474218</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
@@ -4655,117 +4362,110 @@
         <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AK34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>166</v>
+        <v>210</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2020</v>
+        <v>489</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>pacer</t>
+          <t>no event</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>75.0263963989657</v>
+        <v>80.1657274317439</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>22.2753099173553</v>
       </c>
       <c r="E35" t="n">
-        <v>24.6913580246913</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G35" t="n">
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>60</v>
-      </c>
-      <c r="I35" t="inlineStr"/>
+        <v>730.7</v>
+      </c>
+      <c r="I35" t="n">
+        <v>528.2</v>
+      </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>532.5</v>
       </c>
       <c r="K35" t="n">
-        <v>696.8</v>
+        <v>1791.4</v>
       </c>
       <c r="L35" t="n">
-        <v>124.3</v>
+        <v>54.8</v>
       </c>
       <c r="M35" t="n">
-        <v>97.09999999999999</v>
+        <v>170.8</v>
       </c>
       <c r="N35" t="n">
-        <v>918.2</v>
+        <v>136.8</v>
       </c>
       <c r="O35" t="n">
-        <v>56.6</v>
+        <v>362.4</v>
       </c>
       <c r="P35" t="n">
-        <v>31</v>
+        <v>43.9</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.1</v>
+        <v>92.5</v>
       </c>
       <c r="R35" t="n">
-        <v>88.7</v>
+        <v>65.7</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>202.1</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>5.4</v>
+        <v>26.15</v>
       </c>
       <c r="V35" t="n">
-        <v>5.4</v>
+        <v>0.33</v>
       </c>
       <c r="W35" t="n">
-        <v>1</v>
+        <v>26.4833206009677</v>
       </c>
       <c r="X35" t="n">
-        <v>27.2</v>
+        <v>25.4383075422259</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.31055900621118</v>
+        <v>1</v>
       </c>
       <c r="Z35" t="n">
-        <v>28.0430353959766</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>27.1495243336942</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4777,36 +4477,27 @@
         <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AK35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>112</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>236</v>
+        <v>200</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>326</v>
+        <v>467</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -4814,41 +4505,43 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>83.6231034362562</v>
+        <v>80.3545252490684</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>34.7222222222222</v>
       </c>
       <c r="E36" t="n">
-        <v>24.0238086700849</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="G36" t="n">
         <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>45</v>
-      </c>
-      <c r="I36" t="inlineStr"/>
+        <v>319</v>
+      </c>
+      <c r="I36" t="n">
+        <v>274</v>
+      </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>312</v>
       </c>
       <c r="K36" t="n">
-        <v>196.4</v>
+        <v>905</v>
       </c>
       <c r="L36" t="n">
-        <v>35.3</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>124.8</v>
+        <v>20</v>
       </c>
       <c r="N36" t="n">
-        <v>356.5</v>
+        <v>57</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
@@ -4863,31 +4556,31 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="W36" t="n">
-        <v>2</v>
+        <v>28.9661319073084</v>
       </c>
       <c r="X36" t="n">
-        <v>22.9</v>
+        <v>28.31755269249</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.303703703703704</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>23.2365673542144</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>22.6484228950307</v>
+        <v>1</v>
       </c>
       <c r="AB36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4896,37 +4589,28 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>157</v>
-      </c>
-      <c r="AN36" t="inlineStr"/>
+        <v>84</v>
+      </c>
+      <c r="AK36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>607</v>
+        <v>303</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -4934,88 +4618,88 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>83.2043843638299</v>
+        <v>80.4635752718838</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>25.8805706350208</v>
       </c>
       <c r="E37" t="n">
-        <v>30.3673469387755</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>50</v>
+        <v>363</v>
       </c>
       <c r="I37" t="n">
-        <v>1300</v>
+        <v>277</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>141</v>
       </c>
       <c r="K37" t="n">
-        <v>755.3</v>
+        <v>781</v>
       </c>
       <c r="L37" t="n">
-        <v>348.4</v>
+        <v>19</v>
       </c>
       <c r="M37" t="n">
-        <v>608.8</v>
+        <v>15</v>
       </c>
       <c r="N37" t="n">
-        <v>1712.5</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>42.5</v>
+        <v>34</v>
       </c>
       <c r="P37" t="n">
-        <v>76.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>114.3</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>232.9</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>11.9</v>
+        <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>48.6</v>
+        <v>24.3</v>
       </c>
       <c r="V37" t="n">
-        <v>60.5</v>
+        <v>0.22</v>
       </c>
       <c r="W37" t="n">
-        <v>1</v>
+        <v>23.8731856378915</v>
       </c>
       <c r="X37" t="n">
-        <v>25.5</v>
+        <v>23.2036136819621</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.185053380782918</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>25.4329004329004</v>
+        <v>1</v>
       </c>
       <c r="AA37" t="n">
-        <v>24.9660878629553</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
@@ -5027,110 +4711,101 @@
         <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>198</v>
+        <v>212</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>505</v>
+        <v>352</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>no event</t>
+          <t>pacer</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>76.737962962963</v>
+        <v>89.8024340254012</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>27.34375</v>
       </c>
       <c r="E38" t="n">
-        <v>21.8775510204081</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>37</v>
+        <v>325</v>
       </c>
       <c r="I38" t="n">
-        <v>14200</v>
+        <v>230</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="K38" t="n">
-        <v>609</v>
+        <v>654</v>
       </c>
       <c r="L38" t="n">
-        <v>576</v>
+        <v>20</v>
       </c>
       <c r="M38" t="n">
-        <v>358</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1543</v>
+        <v>5</v>
       </c>
       <c r="O38" t="n">
-        <v>203</v>
+        <v>25</v>
       </c>
       <c r="P38" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q38" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>239</v>
+        <v>8</v>
       </c>
       <c r="S38" t="n">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U38" t="n">
-        <v>3</v>
+        <v>21.9</v>
       </c>
       <c r="V38" t="n">
-        <v>66</v>
+        <v>0.32</v>
       </c>
       <c r="W38" t="n">
-        <v>1</v>
+        <v>22.5999490705373</v>
       </c>
       <c r="X38" t="n">
-        <v>26.5</v>
+        <v>21.7511249453965</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.233333333333333</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>26.7379679144385</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>26.2896834807734</v>
+        <v>1</v>
       </c>
       <c r="AB38" t="n">
         <v>0</v>
@@ -5148,33 +4823,24 @@
         <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>134</v>
+        <v>214</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>547</v>
+        <v>329</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -5182,79 +4848,79 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>81.95598904859681</v>
+        <v>85.28495902730251</v>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>21.484375</v>
       </c>
       <c r="E39" t="n">
-        <v>30.8365305317508</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G39" t="n">
         <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="I39" t="n">
-        <v>12400</v>
+        <v>170</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>180</v>
       </c>
       <c r="K39" t="n">
-        <v>381</v>
+        <v>424</v>
       </c>
       <c r="L39" t="n">
-        <v>211</v>
+        <v>26</v>
       </c>
       <c r="M39" t="n">
-        <v>296</v>
+        <v>51</v>
       </c>
       <c r="N39" t="n">
-        <v>888</v>
+        <v>14</v>
       </c>
       <c r="O39" t="n">
-        <v>44</v>
+        <v>91</v>
       </c>
       <c r="P39" t="n">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>102</v>
+        <v>10</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>22.13</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="W39" t="n">
-        <v>1</v>
+        <v>21.9633307868602</v>
       </c>
       <c r="X39" t="n">
-        <v>23.55</v>
+        <v>21.406057760656</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.358885017421603</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>24.8281130634072</v>
+        <v>1</v>
       </c>
       <c r="AA39" t="n">
-        <v>23.7190110408896</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
         <v>0</v>
@@ -5272,31 +4938,24 @@
         <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="AK39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>98</v>
-      </c>
-      <c r="AN39" t="inlineStr"/>
+        <v>120</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>796</v>
+        <v>2847</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -5304,83 +4963,85 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>77.90669860825921</v>
+        <v>83.10646231018831</v>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>29.8649584487534</v>
       </c>
       <c r="E40" t="n">
-        <v>28.125</v>
+        <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G40" t="n">
         <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>60</v>
-      </c>
-      <c r="I40" t="inlineStr"/>
+        <v>156</v>
+      </c>
+      <c r="I40" t="n">
+        <v>197</v>
+      </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>235</v>
       </c>
       <c r="K40" t="n">
-        <v>58.9</v>
+        <v>588</v>
       </c>
       <c r="L40" t="n">
-        <v>34.8</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>65.40000000000001</v>
+        <v>51</v>
       </c>
       <c r="N40" t="n">
-        <v>159.1</v>
+        <v>241</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>292</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q40" t="n">
-        <v>16.8</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>16.8</v>
+        <v>193</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>20.05</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="W40" t="n">
-        <v>2</v>
+        <v>20.7855869620576</v>
       </c>
       <c r="X40" t="n">
-        <v>22.15</v>
+        <v>20.1786711448505</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.24901185770751</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>21.9314998726763</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>21.5128218033123</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -5389,7 +5050,7 @@
         <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -5401,110 +5062,101 @@
         <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>76</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>138</v>
+        <v>114</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>688</v>
+        <v>2121</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>no event</t>
+          <t>pacer</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>86.5826564757776</v>
+        <v>82.77180653788631</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>23.0300453514739</v>
       </c>
       <c r="E41" t="n">
-        <v>28.7639710716633</v>
+        <v>1</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>2860</v>
+        <v>56.6</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>67.3</v>
       </c>
       <c r="K41" t="n">
-        <v>480</v>
+        <v>123.9</v>
       </c>
       <c r="L41" t="n">
-        <v>240.2</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>281.9</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1002.1</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>46.7</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>37.1</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>104.8</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>22.8</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W41" t="n">
-        <v>2</v>
+        <v>22.5681181563535</v>
       </c>
       <c r="X41" t="n">
-        <v>22.25</v>
+        <v>22.1942730679895</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.176229508196721</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>22.2498090145149</v>
+        <v>1</v>
       </c>
       <c r="AA41" t="n">
-        <v>22.0244421422418</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD41" t="n">
         <v>0</v>
@@ -5513,7 +5165,7 @@
         <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -5525,24 +5177,13 @@
         <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>84</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>154</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="AK41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>294</v>
+        <v>702</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -5550,86 +5191,88 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>85.3537317793495</v>
+        <v>79.79584759297281</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>22.3863142771225</v>
       </c>
       <c r="E42" t="n">
-        <v>22.9590876585494</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G42" t="n">
         <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>60</v>
-      </c>
-      <c r="I42" t="inlineStr"/>
+        <v>692</v>
+      </c>
+      <c r="I42" t="n">
+        <v>591</v>
+      </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>166</v>
       </c>
       <c r="K42" t="n">
-        <v>628</v>
+        <v>1449</v>
       </c>
       <c r="L42" t="n">
-        <v>245</v>
+        <v>82</v>
       </c>
       <c r="M42" t="n">
-        <v>383</v>
+        <v>51</v>
       </c>
       <c r="N42" t="n">
-        <v>1256</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>6.3</v>
+        <v>133</v>
       </c>
       <c r="P42" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="Q42" t="n">
-        <v>157</v>
+        <v>11</v>
       </c>
       <c r="R42" t="n">
-        <v>184.3</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>94</v>
+        <v>24.6</v>
       </c>
       <c r="V42" t="n">
-        <v>94</v>
+        <v>0.27</v>
       </c>
       <c r="W42" t="n">
-        <v>2</v>
+        <v>25.4647313470843</v>
       </c>
       <c r="X42" t="n">
-        <v>25.15</v>
+        <v>24.8459903311873</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.235087719298246</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>25.9103641456583</v>
+        <v>1</v>
       </c>
       <c r="AA42" t="n">
-        <v>25.3028496612552</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -5638,118 +5281,113 @@
         <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AK42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN42" t="inlineStr"/>
+        <v>116</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2178</v>
+        <v>452</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>pacer</t>
+          <t>no event</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>79.7736672624027</v>
+        <v>75.6426521345096</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>31.4359113034072</v>
       </c>
       <c r="E43" t="n">
-        <v>30.0432622977087</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G43" t="n">
         <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>60</v>
-      </c>
-      <c r="I43" t="inlineStr"/>
+        <v>679</v>
+      </c>
+      <c r="I43" t="n">
+        <v>324</v>
+      </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="K43" t="n">
-        <v>545.4</v>
+        <v>1087</v>
       </c>
       <c r="L43" t="n">
-        <v>113.2</v>
+        <v>18.7</v>
       </c>
       <c r="M43" t="n">
-        <v>43.6</v>
+        <v>27</v>
       </c>
       <c r="N43" t="n">
-        <v>702.2</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>62.3</v>
+        <v>45.7</v>
       </c>
       <c r="P43" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>69.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>16.8</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>24.3</v>
       </c>
       <c r="V43" t="n">
-        <v>16.8</v>
+        <v>0.26</v>
       </c>
       <c r="W43" t="n">
-        <v>2</v>
+        <v>24.0641711229947</v>
       </c>
       <c r="X43" t="n">
-        <v>25.1</v>
+        <v>23.2857506244092</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.181159420289855</v>
+        <v>1</v>
       </c>
       <c r="Z43" t="n">
-        <v>25.3374076903489</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>24.9966585942398</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>
@@ -5758,155 +5396,139 @@
         <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>96</v>
-      </c>
-      <c r="AN43" t="inlineStr"/>
+        <v>164</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2359</v>
+        <v>2257</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>pacer</t>
+          <t>no event</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>84.26097786270191</v>
+        <v>68.1240494207418</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>24.4897959183673</v>
       </c>
       <c r="E44" t="n">
-        <v>24.2214532871972</v>
+        <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>38.4</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>60</v>
+        <v>338.1</v>
       </c>
       <c r="I44" t="n">
-        <v>4510</v>
+        <v>245.5</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>290.6</v>
       </c>
       <c r="K44" t="n">
-        <v>376.3</v>
+        <v>874.2</v>
       </c>
       <c r="L44" t="n">
-        <v>779</v>
+        <v>61.6</v>
       </c>
       <c r="M44" t="n">
-        <v>320.1</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>1475.4</v>
+        <v>13.8</v>
       </c>
       <c r="O44" t="n">
-        <v>140.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="P44" t="n">
-        <v>42.8</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>89.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>272.6</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>34.4</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>3.1</v>
+        <v>27.65</v>
       </c>
       <c r="V44" t="n">
-        <v>37.5</v>
+        <v>0.17</v>
       </c>
       <c r="W44" t="n">
-        <v>1</v>
+        <v>27.2154316271963</v>
       </c>
       <c r="X44" t="n">
-        <v>24.35</v>
+        <v>26.9211850934372</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.314878892733564</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>24.5734657499363</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>23.6975361509812</v>
+        <v>1</v>
       </c>
       <c r="AB44" t="n">
         <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF44" t="n">
         <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>134</v>
-      </c>
-      <c r="AN44" t="n">
-        <v>136</v>
+        <v>182</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2257</v>
+        <v>1227</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -5914,77 +5536,79 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>68.1240494207418</v>
+        <v>86.8977646905975</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>23.3843537414965</v>
       </c>
       <c r="E45" t="n">
-        <v>24.4897959183673</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G45" t="n">
         <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="I45" t="inlineStr"/>
+        <v>646</v>
+      </c>
+      <c r="I45" t="n">
+        <v>212</v>
+      </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="K45" t="n">
-        <v>338.1</v>
+        <v>973</v>
       </c>
       <c r="L45" t="n">
-        <v>245.5</v>
+        <v>78</v>
       </c>
       <c r="M45" t="n">
-        <v>290.6</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>874.2</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>61.6</v>
+        <v>78</v>
       </c>
       <c r="P45" t="n">
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>75.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>23.2</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="W45" t="n">
-        <v>1</v>
+        <v>22.9182582123759</v>
       </c>
       <c r="X45" t="n">
-        <v>27.65</v>
+        <v>22.1655797488585</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.16887417218543</v>
+        <v>1</v>
       </c>
       <c r="Z45" t="n">
-        <v>27.2154316271963</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>26.9211850934372</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
         <v>0</v>
@@ -5993,134 +5617,125 @@
         <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>138</v>
-      </c>
-      <c r="AN45" t="n">
-        <v>182</v>
+        <v>242</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1705</v>
+        <v>1496</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>no event</t>
+          <t>pacer</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>85.11794274596291</v>
+        <v>87.1905014006135</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>26.0275824770146</v>
       </c>
       <c r="E46" t="n">
-        <v>23.0400201994697</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G46" t="n">
         <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>30</v>
+        <v>756.1</v>
       </c>
       <c r="I46" t="n">
-        <v>25500</v>
+        <v>424.9</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>401.2</v>
       </c>
       <c r="K46" t="n">
-        <v>1413.6</v>
+        <v>1582.2</v>
       </c>
       <c r="L46" t="n">
-        <v>1288</v>
+        <v>242.5</v>
       </c>
       <c r="M46" t="n">
-        <v>1236</v>
+        <v>77.3</v>
       </c>
       <c r="N46" t="n">
-        <v>3937.6</v>
+        <v>80.3</v>
       </c>
       <c r="O46" t="n">
-        <v>379</v>
+        <v>400.1</v>
       </c>
       <c r="P46" t="n">
-        <v>126</v>
+        <v>182.4</v>
       </c>
       <c r="Q46" t="n">
-        <v>492</v>
+        <v>1.5</v>
       </c>
       <c r="R46" t="n">
-        <v>997</v>
+        <v>10.3</v>
       </c>
       <c r="S46" t="n">
-        <v>196</v>
+        <v>194.2</v>
       </c>
       <c r="T46" t="n">
-        <v>5.5</v>
+        <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>650</v>
+        <v>28.2</v>
       </c>
       <c r="V46" t="n">
-        <v>851.5</v>
+        <v>0.24</v>
       </c>
       <c r="W46" t="n">
-        <v>1</v>
+        <v>28.2658517952636</v>
       </c>
       <c r="X46" t="n">
-        <v>30.15</v>
+        <v>27.8049959638069</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.161585365853658</v>
+        <v>1</v>
       </c>
       <c r="Z46" t="n">
-        <v>29.8892284186402</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>29.6417868004739</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF46" t="n">
         <v>0</v>
@@ -6135,24 +5750,15 @@
         <v>0</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AK46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>176</v>
-      </c>
-      <c r="AN46" t="n">
-        <v>232</v>
+        <v>210</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>706</v>
+        <v>514</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -6160,85 +5766,85 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>78.3421933226861</v>
+        <v>86.1886265115218</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>26.813590449954</v>
       </c>
       <c r="E47" t="n">
-        <v>23.3066800530675</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>60</v>
+        <v>560</v>
       </c>
       <c r="I47" t="n">
-        <v>989</v>
+        <v>108</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>277</v>
       </c>
       <c r="K47" t="n">
-        <v>287.2</v>
+        <v>945</v>
       </c>
       <c r="L47" t="n">
-        <v>232.1</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>196.2</v>
+        <v>5</v>
       </c>
       <c r="N47" t="n">
-        <v>715.5</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>15.7</v>
+        <v>5</v>
       </c>
       <c r="P47" t="n">
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>38.2</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>53.9</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U47" t="n">
-        <v>8</v>
+        <v>21.9</v>
       </c>
       <c r="V47" t="n">
-        <v>8</v>
+        <v>0.3</v>
       </c>
       <c r="W47" t="n">
-        <v>1</v>
+        <v>22.2816399286988</v>
       </c>
       <c r="X47" t="n">
-        <v>20.95</v>
+        <v>20.903660546599</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.209401709401709</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>21.5813598166539</v>
+        <v>1</v>
       </c>
       <c r="AA47" t="n">
-        <v>21.1999238701354</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD47" t="n">
         <v>0</v>
@@ -6247,36 +5853,27 @@
         <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM47" t="n">
-        <v>92</v>
-      </c>
-      <c r="AN47" t="n">
-        <v>162</v>
+        <v>186</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2073</v>
+        <v>621</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -6284,86 +5881,88 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>86.328758302279</v>
+        <v>90.7882052817705</v>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>28.734672057202</v>
       </c>
       <c r="E48" t="n">
-        <v>33.6326530612244</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>60</v>
-      </c>
-      <c r="I48" t="inlineStr"/>
+        <v>596</v>
+      </c>
+      <c r="I48" t="n">
+        <v>430</v>
+      </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>384</v>
       </c>
       <c r="K48" t="n">
-        <v>1095.3</v>
+        <v>1410</v>
       </c>
       <c r="L48" t="n">
-        <v>600</v>
+        <v>76</v>
       </c>
       <c r="M48" t="n">
-        <v>673.8</v>
+        <v>25</v>
       </c>
       <c r="N48" t="n">
-        <v>2369.1</v>
+        <v>84</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="P48" t="n">
-        <v>31.4</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>31.4</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>26.4</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="W48" t="n">
-        <v>1</v>
+        <v>26.4196587726</v>
       </c>
       <c r="X48" t="n">
-        <v>30.35</v>
+        <v>25.8994624442976</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.149390243902439</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>29.9847211611918</v>
+        <v>1</v>
       </c>
       <c r="AA48" t="n">
-        <v>29.7211204525439</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
         <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE48" t="n">
         <v>0</v>
@@ -6381,24 +5980,15 @@
         <v>0</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AK48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>108</v>
-      </c>
-      <c r="AN48" t="n">
-        <v>242</v>
+        <v>214</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>851</v>
+        <v>2106</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -6406,91 +5996,91 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>80.950914771719</v>
+        <v>87.3656652597156</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>29.0858725761772</v>
       </c>
       <c r="E49" t="n">
-        <v>31.5616715061229</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>60</v>
+        <v>327.7</v>
       </c>
       <c r="I49" t="n">
-        <v>572</v>
+        <v>332.3</v>
       </c>
       <c r="J49" t="n">
-        <v>1</v>
+        <v>320.1</v>
       </c>
       <c r="K49" t="n">
-        <v>108</v>
+        <v>980.1</v>
       </c>
       <c r="L49" t="n">
-        <v>356</v>
+        <v>19.5</v>
       </c>
       <c r="M49" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>636</v>
+        <v>39</v>
       </c>
       <c r="O49" t="n">
-        <v>10</v>
+        <v>58.5</v>
       </c>
       <c r="P49" t="n">
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>27.45</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="W49" t="n">
-        <v>1</v>
+        <v>27.0244461420932</v>
       </c>
       <c r="X49" t="n">
-        <v>27.15</v>
+        <v>26.4032150535234</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.26517571884984</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>28.0112044817927</v>
+        <v>1</v>
       </c>
       <c r="AA49" t="n">
-        <v>27.5197145882761</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
         <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF49" t="n">
         <v>0</v>
@@ -6505,22 +6095,13 @@
         <v>0</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>108</v>
-      </c>
-      <c r="AN49" t="inlineStr"/>
+        <v>112</v>
+      </c>
+      <c r="AK49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>520</v>
+        <v>700</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -6528,121 +6109,114 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>91.96256179177119</v>
+        <v>86.8191345349456</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>25.6055363321799</v>
       </c>
       <c r="E50" t="n">
-        <v>24.4646016033723</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G50" t="n">
         <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>31</v>
+        <v>420</v>
       </c>
       <c r="I50" t="n">
-        <v>17300</v>
+        <v>285</v>
       </c>
       <c r="J50" t="n">
-        <v>1</v>
+        <v>308</v>
       </c>
       <c r="K50" t="n">
-        <v>503</v>
+        <v>1013</v>
       </c>
       <c r="L50" t="n">
-        <v>648</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>259</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>1410</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W50" t="n">
+        <v>23.554876496053</v>
+      </c>
+      <c r="X50" t="n">
+        <v>23.4220054480732</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>92</v>
+      </c>
+      <c r="AK50" t="n">
         <v>190</v>
       </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" t="n">
-        <v>152</v>
-      </c>
-      <c r="V50" t="n">
-        <v>152</v>
-      </c>
-      <c r="W50" t="n">
-        <v>2</v>
-      </c>
-      <c r="X50" t="n">
-        <v>23.95</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>0.270758122743682</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>23.8731856378915</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>22.9831467948561</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>105</v>
-      </c>
-      <c r="AN50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>550</v>
+        <v>320</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -6650,79 +6224,79 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>82.4873716632443</v>
+        <v>80.3924023373134</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>22.189349112426</v>
       </c>
       <c r="E51" t="n">
-        <v>24.4897959183673</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G51" t="n">
         <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="I51" t="n">
-        <v>18300</v>
+        <v>145</v>
       </c>
       <c r="J51" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="K51" t="n">
-        <v>694</v>
+        <v>322</v>
       </c>
       <c r="L51" t="n">
-        <v>856</v>
+        <v>15</v>
       </c>
       <c r="M51" t="n">
-        <v>1059</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>2609</v>
+        <v>5</v>
       </c>
       <c r="O51" t="n">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="P51" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>20.75</v>
       </c>
       <c r="V51" t="n">
-        <v>11</v>
+        <v>0.25</v>
       </c>
       <c r="W51" t="n">
-        <v>1</v>
+        <v>21.3267125031831</v>
       </c>
       <c r="X51" t="n">
-        <v>25.3</v>
+        <v>20.6802165106906</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.255172413793103</v>
+        <v>1</v>
       </c>
       <c r="Z51" t="n">
-        <v>26.4196587726</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>25.6028939368547</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
         <v>0</v>
@@ -6740,268 +6314,19 @@
         <v>0</v>
       </c>
       <c r="AG51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="AK51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>126</v>
-      </c>
-      <c r="AN51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>2482</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>pacer</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>78.8975567850534</v>
-      </c>
-      <c r="D52" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" t="n">
-        <v>27.7176852352623</v>
-      </c>
-      <c r="F52" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" t="n">
-        <v>1</v>
-      </c>
-      <c r="H52" t="n">
-        <v>60</v>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="n">
-        <v>314.2</v>
-      </c>
-      <c r="L52" t="n">
-        <v>160.8</v>
-      </c>
-      <c r="M52" t="n">
-        <v>322.6</v>
-      </c>
-      <c r="N52" t="n">
-        <v>797.6</v>
-      </c>
-      <c r="O52" t="n">
-        <v>11</v>
-      </c>
-      <c r="P52" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="R52" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="S52" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" t="n">
-        <v>0</v>
-      </c>
-      <c r="U52" t="n">
-        <v>0</v>
-      </c>
-      <c r="V52" t="n">
-        <v>0</v>
-      </c>
-      <c r="W52" t="n">
-        <v>1</v>
-      </c>
-      <c r="X52" t="n">
-        <v>23.25</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>0.245283018867924</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>23.3638910109498</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>22.8665507818143</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM52" t="n">
-        <v>98</v>
-      </c>
-      <c r="AN52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>303</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>no event</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>80.4635752718838</v>
-      </c>
-      <c r="D53" t="n">
-        <v>1</v>
-      </c>
-      <c r="E53" t="n">
-        <v>25.8805706350208</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="n">
-        <v>60</v>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="n">
-        <v>1</v>
-      </c>
-      <c r="K53" t="n">
-        <v>363</v>
-      </c>
-      <c r="L53" t="n">
-        <v>277</v>
-      </c>
-      <c r="M53" t="n">
-        <v>141</v>
-      </c>
-      <c r="N53" t="n">
-        <v>781</v>
-      </c>
-      <c r="O53" t="n">
-        <v>19</v>
-      </c>
-      <c r="P53" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" t="n">
-        <v>34</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" t="n">
-        <v>0</v>
-      </c>
-      <c r="W53" t="n">
-        <v>1</v>
-      </c>
-      <c r="X53" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>0.21978021978022</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>23.8731856378915</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>23.2036136819621</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM53" t="n">
-        <v>88</v>
-      </c>
-      <c r="AN53" t="n">
-        <v>212</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
